--- a/AAII_Financials/Quarterly/TPET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TPET_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
   <si>
     <t>TPET</t>
   </si>
@@ -656,67 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -750,8 +754,11 @@
       <c r="M8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -785,8 +792,11 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -820,8 +830,11 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -835,34 +848,35 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
         <v>200</v>
       </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
+      <c r="F12" s="3">
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
@@ -870,8 +884,11 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,8 +922,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -940,8 +960,11 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -960,12 +983,12 @@
       <c r="H15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3">
         <v>400</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
       </c>
@@ -975,8 +998,11 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -987,43 +1013,47 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E17" s="3">
         <v>2200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>300</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1031,34 +1061,37 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1072,8 +1105,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1081,11 +1115,11 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1093,13 +1127,13 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
@@ -1107,8 +1141,11 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1142,8 +1179,11 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1151,25 +1191,25 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
-      </c>
-      <c r="I22" s="3">
-        <v>100</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>100</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
@@ -1177,43 +1217,49 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2200</v>
+        <v>-1300</v>
       </c>
       <c r="E23" s="3">
         <v>-2200</v>
       </c>
       <c r="F23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="G23" s="3">
         <v>-800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-700</v>
       </c>
       <c r="H23" s="3">
         <v>-700</v>
       </c>
       <c r="I23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J23" s="3">
         <v>-2000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1247,8 +1293,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1282,78 +1331,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2200</v>
+        <v>-1300</v>
       </c>
       <c r="E26" s="3">
         <v>-2200</v>
       </c>
       <c r="F26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="G26" s="3">
         <v>-800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-700</v>
       </c>
       <c r="H26" s="3">
         <v>-700</v>
       </c>
       <c r="I26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2200</v>
+        <v>-1300</v>
       </c>
       <c r="E27" s="3">
         <v>-2200</v>
       </c>
       <c r="F27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="G27" s="3">
         <v>-800</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-700</v>
       </c>
       <c r="H27" s="3">
         <v>-700</v>
       </c>
       <c r="I27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1387,8 +1445,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1422,8 +1483,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1457,8 +1521,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1492,8 +1559,11 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1501,11 +1571,11 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -1513,13 +1583,13 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>1300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
@@ -1527,43 +1597,49 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2200</v>
+        <v>-1300</v>
       </c>
       <c r="E33" s="3">
         <v>-2200</v>
       </c>
       <c r="F33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="G33" s="3">
         <v>-800</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-700</v>
       </c>
       <c r="H33" s="3">
         <v>-700</v>
       </c>
       <c r="I33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1597,83 +1673,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2200</v>
+        <v>-1300</v>
       </c>
       <c r="E35" s="3">
         <v>-2200</v>
       </c>
       <c r="F35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="G35" s="3">
         <v>-800</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-700</v>
       </c>
       <c r="H35" s="3">
         <v>-700</v>
       </c>
       <c r="I35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1687,8 +1772,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1702,32 +1788,33 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2200</v>
-      </c>
-      <c r="F41" s="3">
-        <v>100</v>
       </c>
       <c r="G41" s="3">
         <v>100</v>
       </c>
       <c r="H41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
         <v>200</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,8 +1824,11 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1772,8 +1862,11 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1807,8 +1900,11 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1842,8 +1938,11 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1854,20 +1953,20 @@
         <v>100</v>
       </c>
       <c r="F45" s="3">
+        <v>100</v>
+      </c>
+      <c r="G45" s="3">
         <v>2000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1877,32 +1976,35 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1200</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1912,8 +2014,11 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1947,19 +2052,22 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E48" s="3">
         <v>9000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7300</v>
-      </c>
-      <c r="F48" s="3">
-        <v>5800</v>
       </c>
       <c r="G48" s="3">
         <v>5800</v>
@@ -1968,11 +2076,11 @@
         <v>5800</v>
       </c>
       <c r="I48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J48" s="3">
         <v>7500</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1982,8 +2090,11 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2017,8 +2128,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2052,8 +2166,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2087,19 +2204,22 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
         <v>500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1400</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1900</v>
       </c>
       <c r="G52" s="3">
         <v>1900</v>
@@ -2107,8 +2227,8 @@
       <c r="H52" s="3">
         <v>1900</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="I52" s="3">
+        <v>1900</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2122,8 +2242,11 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2157,32 +2280,35 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E54" s="3">
         <v>11200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8700</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,8 +2318,11 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2207,8 +2336,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2222,32 +2352,33 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2257,32 +2388,35 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>5900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4200</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2292,8 +2426,11 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2304,19 +2441,19 @@
         <v>0</v>
       </c>
       <c r="F59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3">
         <v>100</v>
       </c>
       <c r="H59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I59" s="3">
         <v>0</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+      <c r="J59" s="3">
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2327,32 +2464,35 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E60" s="3">
         <v>800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4600</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2362,8 +2502,11 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2397,13 +2540,16 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E62" s="3">
         <v>100</v>
@@ -2415,13 +2561,13 @@
         <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2432,8 +2578,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2467,8 +2616,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2502,8 +2654,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2537,32 +2692,35 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E66" s="3">
         <v>900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4600</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2572,8 +2730,11 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2587,8 +2748,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2622,8 +2784,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2657,8 +2822,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2692,8 +2860,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2727,32 +2898,35 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-9100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-7000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-4700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2500</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2762,8 +2936,11 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2797,8 +2974,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2832,8 +3012,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2867,32 +3050,35 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E76" s="3">
         <v>10300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4100</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2902,8 +3088,11 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2937,83 +3126,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2200</v>
+        <v>-1300</v>
       </c>
       <c r="E81" s="3">
         <v>-2200</v>
       </c>
       <c r="F81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="G81" s="3">
         <v>-800</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-700</v>
       </c>
       <c r="H81" s="3">
         <v>-700</v>
       </c>
       <c r="I81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3027,8 +3225,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3062,8 +3261,11 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3097,8 +3299,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3132,8 +3337,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3167,8 +3375,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3202,8 +3413,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3237,43 +3451,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-200</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-100</v>
       </c>
       <c r="H89" s="3">
         <v>-100</v>
       </c>
       <c r="I89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J89" s="3">
         <v>100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3287,13 +3507,14 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -3322,8 +3543,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3357,8 +3581,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3392,22 +3619,25 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1000</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3415,20 +3645,23 @@
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3442,8 +3675,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3477,8 +3711,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3512,8 +3749,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3547,8 +3787,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3582,8 +3825,11 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3591,34 +3837,37 @@
         <v>1900</v>
       </c>
       <c r="E100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F100" s="3">
         <v>3600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3652,39 +3901,45 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2100</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TPET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TPET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
   <si>
     <t>TPET</t>
   </si>
@@ -656,71 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -757,8 +761,11 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -795,8 +802,11 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -833,8 +843,11 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,37 +862,38 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
+      <c r="G12" s="3">
+        <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
@@ -887,8 +901,11 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,8 +942,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -963,8 +983,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -986,12 +1009,12 @@
       <c r="I15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K15" s="3">
         <v>400</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1001,8 +1024,11 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1014,46 +1040,50 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>300</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1061,37 +1091,40 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1106,8 +1139,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1118,11 +1152,11 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1130,13 +1164,13 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1144,8 +1178,11 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1182,37 +1219,40 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>500</v>
-      </c>
-      <c r="J22" s="3">
-        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>100</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
@@ -1220,46 +1260,52 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1300</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-2200</v>
       </c>
       <c r="F23" s="3">
         <v>-2200</v>
       </c>
       <c r="G23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H23" s="3">
         <v>-800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-700</v>
       </c>
       <c r="I23" s="3">
         <v>-700</v>
       </c>
       <c r="J23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K23" s="3">
         <v>-2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-400</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1296,8 +1342,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1334,84 +1383,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1300</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-2200</v>
       </c>
       <c r="F26" s="3">
         <v>-2200</v>
       </c>
       <c r="G26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H26" s="3">
         <v>-800</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-700</v>
       </c>
       <c r="I26" s="3">
         <v>-700</v>
       </c>
       <c r="J26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-400</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1300</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-2200</v>
       </c>
       <c r="F27" s="3">
         <v>-2200</v>
       </c>
       <c r="G27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H27" s="3">
         <v>-800</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-700</v>
       </c>
       <c r="I27" s="3">
         <v>-700</v>
       </c>
       <c r="J27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-400</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1448,8 +1506,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1486,8 +1547,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1524,8 +1588,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1562,8 +1629,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1574,11 +1644,11 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -1586,13 +1656,13 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>1300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1600,46 +1670,52 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1300</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-2200</v>
       </c>
       <c r="F33" s="3">
         <v>-2200</v>
       </c>
       <c r="G33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H33" s="3">
         <v>-800</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-700</v>
       </c>
       <c r="I33" s="3">
         <v>-700</v>
       </c>
       <c r="J33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-400</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1676,89 +1752,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1300</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-2200</v>
       </c>
       <c r="F35" s="3">
         <v>-2200</v>
       </c>
       <c r="G35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H35" s="3">
         <v>-800</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-700</v>
       </c>
       <c r="I35" s="3">
         <v>-700</v>
       </c>
       <c r="J35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-400</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1773,8 +1858,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1789,35 +1875,36 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>100</v>
       </c>
       <c r="H41" s="3">
         <v>100</v>
       </c>
       <c r="I41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>200</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1827,8 +1914,11 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1865,8 +1955,11 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1903,8 +1996,11 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1941,8 +2037,11 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1956,20 +2055,20 @@
         <v>100</v>
       </c>
       <c r="G45" s="3">
+        <v>100</v>
+      </c>
+      <c r="H45" s="3">
         <v>2000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1979,35 +2078,38 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1200</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,8 +2119,11 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2055,22 +2160,25 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E48" s="3">
         <v>9900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>5800</v>
       </c>
       <c r="H48" s="3">
         <v>5800</v>
@@ -2079,11 +2187,11 @@
         <v>5800</v>
       </c>
       <c r="J48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K48" s="3">
         <v>7500</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2093,8 +2201,11 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2131,8 +2242,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2169,8 +2283,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2207,22 +2324,25 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
         <v>500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1900</v>
       </c>
       <c r="H52" s="3">
         <v>1900</v>
@@ -2230,8 +2350,8 @@
       <c r="I52" s="3">
         <v>1900</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="J52" s="3">
+        <v>1900</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2245,8 +2365,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2283,35 +2406,38 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E54" s="3">
         <v>11600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8700</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2321,8 +2447,11 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2337,8 +2466,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2353,8 +2483,9 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2362,26 +2493,26 @@
         <v>600</v>
       </c>
       <c r="E57" s="3">
+        <v>600</v>
+      </c>
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2391,35 +2522,38 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1200</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>5900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4200</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2429,13 +2563,16 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
@@ -2444,19 +2581,19 @@
         <v>0</v>
       </c>
       <c r="G59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3">
         <v>100</v>
       </c>
       <c r="I59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J59" s="3">
         <v>0</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
+      <c r="K59" s="3">
+        <v>0</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
@@ -2467,8 +2604,11 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2476,26 +2616,26 @@
         <v>1900</v>
       </c>
       <c r="E60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F60" s="3">
         <v>800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,8 +2645,11 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2543,16 +2686,19 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
@@ -2564,13 +2710,13 @@
         <v>100</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
+      <c r="K62" s="3">
+        <v>0</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
@@ -2581,8 +2727,11 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2619,8 +2768,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2657,8 +2809,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2695,35 +2850,38 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4600</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2733,8 +2891,11 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2749,8 +2910,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2787,8 +2949,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2825,8 +2990,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2863,8 +3031,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2901,35 +3072,38 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-9100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2939,8 +3113,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2977,8 +3154,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3015,8 +3195,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3053,35 +3236,38 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4100</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,8 +3277,11 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3129,89 +3318,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1300</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-2200</v>
       </c>
       <c r="F81" s="3">
         <v>-2200</v>
       </c>
       <c r="G81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H81" s="3">
         <v>-800</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-700</v>
       </c>
       <c r="I81" s="3">
         <v>-700</v>
       </c>
       <c r="J81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-400</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3226,8 +3424,9 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3264,8 +3463,11 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3302,8 +3504,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3340,8 +3545,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3378,8 +3586,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3416,8 +3627,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3454,46 +3668,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-200</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-100</v>
       </c>
       <c r="I89" s="3">
         <v>-100</v>
       </c>
       <c r="J89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K89" s="3">
         <v>100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3508,17 +3728,18 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -3546,8 +3767,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3584,8 +3808,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3622,25 +3849,28 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1000</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -3648,20 +3878,23 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3676,8 +3909,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3714,8 +3948,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3752,8 +3989,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3790,8 +4030,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3828,46 +4071,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1900</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
         <v>1900</v>
       </c>
       <c r="F100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G100" s="3">
         <v>3600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3904,42 +4153,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TPET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TPET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
   <si>
     <t>TPET</t>
   </si>
@@ -656,75 +656,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -732,22 +739,22 @@
         <v>3</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -764,8 +771,14 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -805,16 +818,22 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>100</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
@@ -846,8 +865,14 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,22 +888,24 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>100</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3">
-        <v>200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -886,8 +913,8 @@
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="3">
-        <v>0</v>
+      <c r="J12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -898,14 +925,20 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
+      <c r="N12" s="3">
+        <v>0</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,31 +978,37 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>1100</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -986,49 +1025,61 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3">
         <v>400</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1041,90 +1092,104 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>200</v>
-      </c>
-      <c r="I17" s="3">
-        <v>100</v>
       </c>
       <c r="J17" s="3">
         <v>200</v>
       </c>
       <c r="K17" s="3">
+        <v>100</v>
+      </c>
+      <c r="L17" s="3">
+        <v>200</v>
+      </c>
+      <c r="M17" s="3">
         <v>600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-1500</v>
       </c>
       <c r="E18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G18" s="3">
         <v>-1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-100</v>
       </c>
       <c r="J18" s="3">
         <v>-200</v>
       </c>
       <c r="K18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,13 +1205,15 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1155,57 +1222,63 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-1100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-200</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1222,113 +1295,131 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-2200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1345,8 +1436,14 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1386,90 +1483,108 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-2200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-2200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-400</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1509,8 +1624,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1671,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1591,8 +1718,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,13 +1765,19 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -1647,75 +1786,87 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>1300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-2200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-400</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1755,95 +1906,113 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-2200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-400</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1859,8 +2028,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1876,8 +2047,10 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1885,40 +2058,46 @@
         <v>300</v>
       </c>
       <c r="E41" s="3">
+        <v>200</v>
+      </c>
+      <c r="F41" s="3">
+        <v>300</v>
+      </c>
+      <c r="G41" s="3">
         <v>1600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>200</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1958,31 +2137,37 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -1999,31 +2184,37 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2040,113 +2231,131 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K45" s="3">
         <v>1700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>800</v>
+      </c>
+      <c r="F46" s="3">
         <v>500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1200</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2163,49 +2372,61 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F48" s="3">
         <v>10900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>9900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>9000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>7300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>5800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>5800</v>
       </c>
       <c r="J48" s="3">
         <v>5800</v>
       </c>
       <c r="K48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="L48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="M48" s="3">
         <v>7500</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2245,8 +2466,14 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2286,8 +2513,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2327,37 +2560,43 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
         <v>500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1900</v>
       </c>
       <c r="J52" s="3">
         <v>1900</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L52" s="3">
+        <v>1900</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
@@ -2368,8 +2607,14 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2409,49 +2654,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F54" s="3">
         <v>11300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>11600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>11200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>11000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>9800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>9500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>8800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>8700</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2467,8 +2724,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,122 +2743,136 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1400</v>
       </c>
       <c r="I57" s="3">
         <v>1200</v>
       </c>
       <c r="J57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>500</v>
+      </c>
+      <c r="F58" s="3">
         <v>1300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1200</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>5900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>4800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>4200</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
         <v>100</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
       <c r="G59" s="3">
         <v>0</v>
       </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="J59" s="3">
-        <v>0</v>
-      </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
@@ -2607,49 +2880,61 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2689,22 +2974,28 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
         <v>400</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>100</v>
-      </c>
       <c r="G62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
         <v>100</v>
@@ -2713,16 +3004,16 @@
         <v>100</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -2730,8 +3021,14 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2771,8 +3068,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2812,8 +3115,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2853,49 +3162,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F66" s="3">
         <v>2300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>7500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4600</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2911,8 +3232,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2952,8 +3275,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2993,8 +3322,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3034,8 +3369,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3075,49 +3416,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-12100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-10400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-9100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-7000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-4700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-3900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-3200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-2500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3157,8 +3510,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3198,8 +3557,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3239,49 +3604,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9000</v>
+        <v>8100</v>
       </c>
       <c r="E76" s="3">
         <v>9700</v>
       </c>
       <c r="F76" s="3">
+        <v>9000</v>
+      </c>
+      <c r="G76" s="3">
+        <v>9700</v>
+      </c>
+      <c r="H76" s="3">
         <v>10300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>9800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3321,95 +3698,113 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-2200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-400</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3425,31 +3820,33 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3466,8 +3863,14 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3507,8 +3910,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3548,8 +3957,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3589,8 +4004,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3630,8 +4051,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,49 +4098,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-400</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3729,31 +4168,33 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-900</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-1700</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>-1500</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3770,8 +4211,14 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3811,8 +4258,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3852,37 +4305,43 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1000</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
@@ -3890,11 +4349,17 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3910,31 +4375,33 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3951,8 +4418,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3992,8 +4465,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4033,8 +4512,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4074,72 +4559,84 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>1900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>3600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>1100</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4156,45 +4653,57 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>2100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>600</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TPET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TPET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
   <si>
     <t>TPET</t>
   </si>
@@ -656,82 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -741,11 +749,11 @@
       <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
+      <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3">
+        <v>100</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -756,11 +764,11 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -777,8 +785,14 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -824,22 +838,28 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+      <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
+        <v>100</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -871,8 +891,14 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,8 +916,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,8 +947,8 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3">
-        <v>0</v>
+      <c r="L12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
@@ -931,14 +959,20 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
+      <c r="P12" s="3">
+        <v>0</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,37 +1018,43 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>100</v>
       </c>
       <c r="E14" s="3">
+        <v>100</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>1100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>1100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1031,8 +1071,14 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1057,29 +1103,35 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3">
         <v>400</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,102 +1146,116 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F17" s="3">
         <v>1600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2000</v>
       </c>
-      <c r="F17" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I17" s="3">
         <v>1300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>200</v>
-      </c>
-      <c r="K17" s="3">
-        <v>100</v>
       </c>
       <c r="L17" s="3">
         <v>200</v>
       </c>
       <c r="M17" s="3">
+        <v>100</v>
+      </c>
+      <c r="N17" s="3">
+        <v>200</v>
+      </c>
+      <c r="O17" s="3">
         <v>600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1900</v>
       </c>
-      <c r="F18" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-100</v>
       </c>
       <c r="L18" s="3">
         <v>-200</v>
       </c>
       <c r="M18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O18" s="3">
         <v>-600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-300</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,13 +1273,15 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1224,68 +1292,74 @@
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-1300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-2000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-2200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-200</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1301,102 +1375,120 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3">
+        <v>300</v>
+      </c>
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-4000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-400</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1421,11 +1513,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1442,8 +1534,14 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1489,102 +1587,120 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-2200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-400</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-400</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1630,8 +1746,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1799,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1724,8 +1852,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1771,13 +1905,19 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -1788,85 +1928,97 @@
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>1300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-400</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1912,107 +2064,125 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-400</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2030,8 +2200,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2049,55 +2221,63 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E41" s="3">
         <v>300</v>
-      </c>
-      <c r="E41" s="3">
-        <v>200</v>
       </c>
       <c r="F41" s="3">
         <v>300</v>
       </c>
       <c r="G41" s="3">
+        <v>200</v>
+      </c>
+      <c r="H41" s="3">
+        <v>300</v>
+      </c>
+      <c r="I41" s="3">
         <v>1600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
         <v>200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2143,8 +2323,14 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2169,11 +2355,11 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2190,8 +2376,14 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2216,11 +2408,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2237,8 +2429,14 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2260,79 +2458,91 @@
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>1900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E46" s="3">
         <v>600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
+        <v>600</v>
+      </c>
+      <c r="G46" s="3">
         <v>800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1200</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2357,11 +2567,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2378,55 +2588,67 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E48" s="3">
         <v>11100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>11100</v>
+      </c>
+      <c r="G48" s="3">
         <v>11000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>10900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>9900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>9000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7300</v>
-      </c>
-      <c r="J48" s="3">
-        <v>5800</v>
-      </c>
-      <c r="K48" s="3">
-        <v>5800</v>
       </c>
       <c r="L48" s="3">
         <v>5800</v>
       </c>
       <c r="M48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="N48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="O48" s="3">
         <v>7500</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2472,8 +2694,14 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2519,8 +2747,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2566,8 +2800,14 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2583,26 +2823,26 @@
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
         <v>500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1400</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1900</v>
       </c>
       <c r="L52" s="3">
         <v>1900</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N52" s="3">
+        <v>1900</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
@@ -2613,8 +2853,14 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2660,55 +2906,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E54" s="3">
         <v>11700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
+        <v>11700</v>
+      </c>
+      <c r="G54" s="3">
         <v>11800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>11300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>11600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>11200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>9800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>9500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>8800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>8700</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2726,8 +2984,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2745,140 +3005,154 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="E57" s="3">
         <v>1000</v>
       </c>
       <c r="F57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1400</v>
       </c>
       <c r="K57" s="3">
         <v>1200</v>
       </c>
       <c r="L57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>900</v>
+      </c>
+      <c r="F58" s="3">
         <v>1600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1200</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>5900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>5400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>4800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>4200</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>700</v>
+      </c>
+      <c r="F59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
       <c r="I59" s="3">
         <v>0</v>
       </c>
       <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
+        <v>0</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
@@ -2886,55 +3160,67 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F60" s="3">
         <v>3600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>5400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4600</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2980,8 +3266,14 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2989,19 +3281,19 @@
         <v>100</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F62" s="3">
+        <v>100</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>100</v>
-      </c>
       <c r="I62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3">
         <v>100</v>
@@ -3010,16 +3302,16 @@
         <v>100</v>
       </c>
       <c r="L62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
@@ -3027,8 +3319,14 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,8 +3372,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3425,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3168,55 +3478,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F66" s="3">
         <v>3600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>7500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>6800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4600</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3234,8 +3556,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3281,8 +3605,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,8 +3658,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3375,8 +3711,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3422,55 +3764,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-18400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-16200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-12100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-10400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-9100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-7000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-4700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-3900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-3200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-2500</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3516,8 +3870,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3563,8 +3923,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3610,55 +3976,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F76" s="3">
         <v>8100</v>
-      </c>
-      <c r="E76" s="3">
-        <v>9700</v>
-      </c>
-      <c r="F76" s="3">
-        <v>9000</v>
       </c>
       <c r="G76" s="3">
         <v>9700</v>
       </c>
       <c r="H76" s="3">
+        <v>9000</v>
+      </c>
+      <c r="I76" s="3">
+        <v>9700</v>
+      </c>
+      <c r="J76" s="3">
         <v>10300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>9800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>3400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4100</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3704,107 +4082,125 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-400</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3822,8 +4218,10 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3848,11 +4246,11 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -3869,8 +4267,14 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3916,8 +4320,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3963,8 +4373,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4010,8 +4426,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4057,8 +4479,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4104,55 +4532,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4170,8 +4610,10 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4179,28 +4621,28 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1500</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -4217,8 +4659,14 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4264,8 +4712,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4311,43 +4765,49 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1000</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -4355,11 +4815,17 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4377,8 +4843,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4403,11 +4871,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4424,8 +4892,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4471,8 +4945,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4518,8 +4998,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4565,55 +5051,67 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F100" s="3">
         <v>800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>3600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>1100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4638,11 +5136,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4659,51 +5157,63 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>2100</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>600</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TPET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TPET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
   <si>
     <t>TPET</t>
   </si>
@@ -656,90 +656,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -747,7 +750,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
@@ -755,8 +758,8 @@
       <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
+      <c r="H8" s="3">
+        <v>100</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -770,8 +773,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -791,13 +794,16 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>3</v>
@@ -844,8 +850,11 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -853,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
@@ -861,8 +870,8 @@
       <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
+      <c r="H10" s="3">
+        <v>100</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
@@ -897,8 +906,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,8 +930,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -953,17 +966,17 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3">
-        <v>0</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
@@ -971,8 +984,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,40 +1040,43 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F14" s="3">
+        <v>100</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>1100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>1100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1077,8 +1096,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1109,18 +1131,18 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3">
         <v>400</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1130,8 +1152,11 @@
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,114 +1173,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-300</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,16 +1307,17 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1292,35 +1325,35 @@
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1328,41 +1361,44 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-200</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1381,52 +1417,55 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3">
         <v>300</v>
       </c>
       <c r="F22" s="3">
+        <v>300</v>
+      </c>
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>200</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>500</v>
-      </c>
-      <c r="O22" s="3">
-        <v>100</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>100</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
@@ -1434,8 +1473,11 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1443,52 +1485,55 @@
         <v>-1600</v>
       </c>
       <c r="E23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-2200</v>
       </c>
       <c r="K23" s="3">
         <v>-2200</v>
       </c>
       <c r="L23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M23" s="3">
         <v>-800</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-700</v>
       </c>
       <c r="N23" s="3">
         <v>-700</v>
       </c>
       <c r="O23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P23" s="3">
         <v>-2000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-400</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1519,8 +1564,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1540,8 +1585,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,8 +1641,11 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1602,52 +1653,55 @@
         <v>-1600</v>
       </c>
       <c r="E26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-2200</v>
       </c>
       <c r="K26" s="3">
         <v>-2200</v>
       </c>
       <c r="L26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M26" s="3">
         <v>-800</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-700</v>
       </c>
       <c r="N26" s="3">
         <v>-700</v>
       </c>
       <c r="O26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P26" s="3">
         <v>-2000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1655,52 +1709,55 @@
         <v>-1600</v>
       </c>
       <c r="E27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-2200</v>
       </c>
       <c r="K27" s="3">
         <v>-2200</v>
       </c>
       <c r="L27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M27" s="3">
         <v>-800</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-700</v>
       </c>
       <c r="N27" s="3">
         <v>-700</v>
       </c>
       <c r="O27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P27" s="3">
         <v>-2000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1809,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1865,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1921,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,16 +1977,19 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -1928,35 +1997,35 @@
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>1300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -1964,8 +2033,11 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1973,52 +2045,55 @@
         <v>-1600</v>
       </c>
       <c r="E33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-2200</v>
       </c>
       <c r="K33" s="3">
         <v>-2200</v>
       </c>
       <c r="L33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M33" s="3">
         <v>-800</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-700</v>
       </c>
       <c r="N33" s="3">
         <v>-700</v>
       </c>
       <c r="O33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P33" s="3">
         <v>-2000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,8 +2145,11 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2079,110 +2157,116 @@
         <v>-1600</v>
       </c>
       <c r="E35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-2200</v>
       </c>
       <c r="K35" s="3">
         <v>-2200</v>
       </c>
       <c r="L35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M35" s="3">
         <v>-800</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-700</v>
       </c>
       <c r="N35" s="3">
         <v>-700</v>
       </c>
       <c r="O35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P35" s="3">
         <v>-2000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2286,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,50 +2308,51 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2000</v>
-      </c>
-      <c r="E41" s="3">
-        <v>300</v>
       </c>
       <c r="F41" s="3">
         <v>300</v>
       </c>
       <c r="G41" s="3">
+        <v>300</v>
+      </c>
+      <c r="H41" s="3">
         <v>200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2200</v>
-      </c>
-      <c r="L41" s="3">
-        <v>100</v>
       </c>
       <c r="M41" s="3">
         <v>100</v>
       </c>
       <c r="N41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3">
         <v>200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,8 +2362,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2329,13 +2418,16 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>0</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
@@ -2361,8 +2453,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2382,8 +2474,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2414,8 +2509,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2435,8 +2530,11 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2464,21 +2562,21 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>1900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1000</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2488,50 +2586,53 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2000</v>
-      </c>
-      <c r="E46" s="3">
-        <v>600</v>
       </c>
       <c r="F46" s="3">
         <v>600</v>
       </c>
       <c r="G46" s="3">
+        <v>600</v>
+      </c>
+      <c r="H46" s="3">
         <v>800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1200</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2541,8 +2642,11 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2573,8 +2677,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2594,37 +2698,40 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E48" s="3">
         <v>11200</v>
-      </c>
-      <c r="E48" s="3">
-        <v>11100</v>
       </c>
       <c r="F48" s="3">
         <v>11100</v>
       </c>
       <c r="G48" s="3">
+        <v>11100</v>
+      </c>
+      <c r="H48" s="3">
         <v>11000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7300</v>
-      </c>
-      <c r="L48" s="3">
-        <v>5800</v>
       </c>
       <c r="M48" s="3">
         <v>5800</v>
@@ -2633,11 +2740,11 @@
         <v>5800</v>
       </c>
       <c r="O48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="P48" s="3">
         <v>7500</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,8 +2754,11 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2700,8 +2810,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2866,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,8 +2922,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2829,14 +2948,14 @@
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
         <v>500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1400</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1900</v>
       </c>
       <c r="M52" s="3">
         <v>1900</v>
@@ -2844,8 +2963,8 @@
       <c r="N52" s="3">
         <v>1900</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>1900</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
@@ -2859,8 +2978,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,50 +3034,53 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E54" s="3">
         <v>13200</v>
-      </c>
-      <c r="E54" s="3">
-        <v>11700</v>
       </c>
       <c r="F54" s="3">
         <v>11700</v>
       </c>
       <c r="G54" s="3">
+        <v>11700</v>
+      </c>
+      <c r="H54" s="3">
         <v>11800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8700</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,8 +3090,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3114,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,50 +3136,51 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E57" s="3">
         <v>1000</v>
       </c>
       <c r="F57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>600</v>
       </c>
       <c r="I57" s="3">
         <v>600</v>
       </c>
       <c r="J57" s="3">
+        <v>600</v>
+      </c>
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3060,50 +3190,53 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>600</v>
+      </c>
+      <c r="E58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1200</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>5900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4200</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3113,29 +3246,32 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
         <v>100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
       <c r="J59" s="3">
         <v>0</v>
       </c>
@@ -3143,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="L59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M59" s="3">
         <v>100</v>
       </c>
       <c r="N59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O59" s="3">
         <v>0</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
+      <c r="P59" s="3">
+        <v>0</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
@@ -3166,50 +3302,53 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2000</v>
-      </c>
-      <c r="H60" s="3">
-        <v>1900</v>
       </c>
       <c r="I60" s="3">
         <v>1900</v>
       </c>
       <c r="J60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4600</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,8 +3358,11 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3272,8 +3414,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3287,16 +3432,16 @@
         <v>100</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
         <v>400</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
       <c r="J62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K62" s="3">
         <v>100</v>
@@ -3308,13 +3453,13 @@
         <v>100</v>
       </c>
       <c r="N62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
+      <c r="P62" s="3">
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
@@ -3325,8 +3470,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3526,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3582,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,50 +3638,53 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4600</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3537,8 +3694,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3718,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3772,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3828,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +3884,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,50 +3940,53 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-21700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-20100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-18400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-16200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-12100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-10400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-9100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2500</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3823,8 +3996,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4052,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4108,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,50 +4164,53 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E76" s="3">
         <v>11700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4100</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4035,8 +4220,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,66 +4276,72 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4155,52 +4349,55 @@
         <v>-1600</v>
       </c>
       <c r="E81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-2200</v>
       </c>
       <c r="K81" s="3">
         <v>-2200</v>
       </c>
       <c r="L81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M81" s="3">
         <v>-800</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-700</v>
       </c>
       <c r="N81" s="3">
         <v>-700</v>
       </c>
       <c r="O81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P81" s="3">
         <v>-2000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,8 +4417,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4252,8 +4450,8 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -4273,8 +4471,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4527,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4583,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4639,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4695,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,61 +4751,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-200</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-100</v>
       </c>
       <c r="N89" s="3">
         <v>-100</v>
       </c>
       <c r="O89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P89" s="3">
         <v>100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,40 +4831,41 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>-900</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-900</v>
       </c>
       <c r="J91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1500</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -4665,8 +4885,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4941,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,38 +4997,41 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-500</v>
       </c>
       <c r="H94" s="3">
         <v>-500</v>
       </c>
       <c r="I94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4812,20 +5041,23 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5077,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4877,8 +5110,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4898,8 +5131,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5187,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5243,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,61 +5299,67 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>500</v>
+      </c>
+      <c r="E100" s="3">
         <v>2800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>1900</v>
       </c>
       <c r="J100" s="3">
         <v>1900</v>
       </c>
       <c r="K100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L100" s="3">
         <v>3600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5142,8 +5390,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5163,57 +5411,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E102" s="3">
         <v>1700</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>600</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TPET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TPET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
   <si>
     <t>TPET</t>
   </si>
@@ -656,123 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45412</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45322</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45138</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44957</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44592</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
+      <c r="J8" s="3">
+        <v>100</v>
+      </c>
+      <c r="K8" s="3">
+        <v>100</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
@@ -783,11 +791,11 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -804,8 +812,14 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -813,13 +827,13 @@
         <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -863,8 +877,14 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -872,25 +892,25 @@
         <v>100</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
+      <c r="J10" s="3">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3">
+        <v>100</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
@@ -922,8 +942,14 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,8 +971,10 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -986,8 +1014,8 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3">
-        <v>0</v>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
@@ -998,14 +1026,20 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
+      <c r="T12" s="3">
+        <v>0</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,49 +1097,55 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>100</v>
+      </c>
+      <c r="F14" s="3">
         <v>500</v>
-      </c>
-      <c r="E14" s="3">
-        <v>700</v>
-      </c>
-      <c r="F14" s="3">
-        <v>100</v>
       </c>
       <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>100</v>
       </c>
       <c r="I14" s="3">
+        <v>100</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>1100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1122,8 +1162,14 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1137,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -1160,29 +1206,35 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3">
         <v>400</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,8 +1253,10 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1210,117 +1264,129 @@
         <v>900</v>
       </c>
       <c r="E17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F17" s="3">
         <v>900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H17" s="3">
         <v>1200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1000</v>
-      </c>
-      <c r="N17" s="3">
-        <v>200</v>
-      </c>
-      <c r="O17" s="3">
-        <v>100</v>
       </c>
       <c r="P17" s="3">
         <v>200</v>
       </c>
       <c r="Q17" s="3">
+        <v>100</v>
+      </c>
+      <c r="R17" s="3">
+        <v>200</v>
+      </c>
+      <c r="S17" s="3">
         <v>600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-700</v>
       </c>
-      <c r="E18" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1300</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1900</v>
       </c>
       <c r="J18" s="3">
         <v>-1500</v>
       </c>
       <c r="K18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="M18" s="3">
         <v>-1300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-100</v>
       </c>
       <c r="P18" s="3">
         <v>-200</v>
       </c>
       <c r="Q18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S18" s="3">
         <v>-600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-300</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,22 +1408,24 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1371,80 +1439,86 @@
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1300</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1460,8 +1534,14 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1469,117 +1549,129 @@
         <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
+        <v>100</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>1000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-4000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-400</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1616,11 +1708,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1637,8 +1729,14 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,126 +1794,144 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-400</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1989,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +2054,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2119,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,22 +2184,28 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -2079,97 +2219,109 @@
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>1300</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-400</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,131 +2379,149 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-400</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45412</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45322</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45138</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44957</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44592</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2543,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,67 +2568,75 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>900</v>
+      </c>
+      <c r="F41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
-      </c>
-      <c r="H41" s="3">
-        <v>300</v>
-      </c>
-      <c r="I41" s="3">
-        <v>200</v>
       </c>
       <c r="J41" s="3">
         <v>300</v>
       </c>
       <c r="K41" s="3">
+        <v>200</v>
+      </c>
+      <c r="L41" s="3">
+        <v>300</v>
+      </c>
+      <c r="M41" s="3">
         <v>1600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>100</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3">
         <v>200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2514,22 +2694,28 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+      <c r="F43" s="3">
+        <v>100</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -2552,11 +2738,11 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2573,8 +2759,14 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2611,11 +2803,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2632,8 +2824,14 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2667,32 +2865,38 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>1900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2700,58 +2904,64 @@
         <v>900</v>
       </c>
       <c r="E46" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F46" s="3">
+        <v>900</v>
+      </c>
+      <c r="G46" s="3">
         <v>1700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1200</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2788,11 +2998,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2809,67 +3019,79 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F48" s="3">
         <v>12200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>12000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>11200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>11100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>11100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>11000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>10900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>9900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>9000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>7300</v>
-      </c>
-      <c r="N48" s="3">
-        <v>5800</v>
-      </c>
-      <c r="O48" s="3">
-        <v>5800</v>
       </c>
       <c r="P48" s="3">
         <v>5800</v>
       </c>
       <c r="Q48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="R48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="S48" s="3">
         <v>7500</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2927,8 +3149,14 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3214,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,8 +3279,14 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3074,26 +3314,26 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3">
         <v>500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1400</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1900</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1900</v>
       </c>
       <c r="P52" s="3">
         <v>1900</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
+      <c r="Q52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R52" s="3">
+        <v>1900</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
@@ -3104,8 +3344,14 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,67 +3409,79 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F54" s="3">
         <v>13000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>13800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>13200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>11700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>11700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>11300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>11600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>11200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>11000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>9800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>9500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>8800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>8700</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3503,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,176 +3528,190 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1400</v>
       </c>
       <c r="I57" s="3">
         <v>1000</v>
       </c>
       <c r="J57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
-      </c>
-      <c r="M57" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1400</v>
       </c>
       <c r="O57" s="3">
         <v>1200</v>
       </c>
       <c r="P57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
+        <v>500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>5900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>5400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>4800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>4200</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>100</v>
+      </c>
+      <c r="F59" s="3">
         <v>200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
       <c r="M59" s="3">
         <v>0</v>
       </c>
       <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>100</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
+        <v>0</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
@@ -3445,67 +3719,79 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F60" s="3">
         <v>1600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>5400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>4600</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3563,13 +3849,19 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
         <v>100</v>
@@ -3584,19 +3876,19 @@
         <v>100</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3">
+        <v>100</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>400</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>100</v>
-      </c>
       <c r="M62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
@@ -3605,16 +3897,16 @@
         <v>100</v>
       </c>
       <c r="P62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
@@ -3622,8 +3914,14 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3979,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +4044,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,67 +4109,79 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F66" s="3">
         <v>1600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>7500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>6800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4203,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4264,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4329,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4058,8 +4394,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,67 +4459,79 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-24600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-23300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-21700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-20100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-18400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-16200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-12100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-10400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-9100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-7000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-4700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-3900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-2500</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4589,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4654,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,67 +4719,79 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>11300</v>
+      </c>
+      <c r="F76" s="3">
         <v>11400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>11400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>9000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8100</v>
-      </c>
-      <c r="I76" s="3">
-        <v>9700</v>
-      </c>
-      <c r="J76" s="3">
-        <v>9000</v>
       </c>
       <c r="K76" s="3">
         <v>9700</v>
       </c>
       <c r="L76" s="3">
+        <v>9000</v>
+      </c>
+      <c r="M76" s="3">
+        <v>9700</v>
+      </c>
+      <c r="N76" s="3">
         <v>10300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>9800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4100</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,131 +4849,149 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45412</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45322</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45138</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44957</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44592</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-400</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,8 +5013,10 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4655,11 +5053,11 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -4676,8 +5074,14 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +5139,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +5204,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5269,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5334,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,67 +5399,79 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-4000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,49 +5493,51 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1500</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -5112,8 +5554,14 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5619,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,55 +5684,61 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5286,11 +5746,17 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5778,10 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5350,11 +5818,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5371,8 +5839,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5904,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5969,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,67 +6034,79 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E100" s="3">
+        <v>900</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>2800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>3900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>1900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>3600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>1100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5645,11 +6143,11 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5666,63 +6164,75 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1700</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>2100</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>600</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
